--- a/artfynd/A 49079-2023 artfynd.xlsx
+++ b/artfynd/A 49079-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49079-2023 artfynd.xlsx
+++ b/artfynd/A 49079-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1567,130 +1567,6 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>119570740</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57226</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100067</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Haliaeetus albicilla</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Vid bryggan Försjön, Försjön, Marbäck s:n, Sm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>496986</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6412838</v>
-      </c>
-      <c r="S9" t="n">
-        <v>50</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Aneby</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Askeryd</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49079-2023 artfynd.xlsx
+++ b/artfynd/A 49079-2023 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>126772458</v>
       </c>
       <c r="B9" t="n">
-        <v>57530</v>
+        <v>57534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49079-2023 artfynd.xlsx
+++ b/artfynd/A 49079-2023 artfynd.xlsx
@@ -1572,7 +1572,7 @@
         <v>126772458</v>
       </c>
       <c r="B9" t="n">
-        <v>57534</v>
+        <v>57530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49079-2023 artfynd.xlsx
+++ b/artfynd/A 49079-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85254373</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86534363</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86534162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85253912</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92788959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1393,6 +1423,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69425509</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1514,6 +1549,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69430909</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94366532</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,6 +1773,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974027</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1838,8 +1888,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94343879</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>